--- a/01_Data/01_Derived/labels_2.xlsx
+++ b/01_Data/01_Derived/labels_2.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ee35ec19c0f25579/VP/Las Antioquias/pulso_antioquia/01_Data/01_Derived/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17B8E7BD-7C2A-4E06-B860-C7C5EE05B2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{17B8E7BD-7C2A-4E06-B860-C7C5EE05B2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FD10B7D-C156-45CB-B7C8-D27DE1B87F42}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" iterate="1" iterateCount="1000" calcOnSave="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="410">
   <si>
     <t>terms</t>
   </si>
@@ -1208,6 +1208,48 @@
   </si>
   <si>
     <t>Suicidios 15–64 x100k</t>
+  </si>
+  <si>
+    <t>Índice envejecimiento (rural)</t>
+  </si>
+  <si>
+    <t>Índice envejecimiento H (rural)</t>
+  </si>
+  <si>
+    <t>Índice envejecimiento M (rural)</t>
+  </si>
+  <si>
+    <t>i_enve_h_r</t>
+  </si>
+  <si>
+    <t>i_enve_m_r</t>
+  </si>
+  <si>
+    <t>i_enve_t_r</t>
+  </si>
+  <si>
+    <t>tasa_iam</t>
+  </si>
+  <si>
+    <t>Mortalidad IAM x100k</t>
+  </si>
+  <si>
+    <t>ide_t_r</t>
+  </si>
+  <si>
+    <t>ide_h_r</t>
+  </si>
+  <si>
+    <t>ide_m_r</t>
+  </si>
+  <si>
+    <t>Índice dep. econ. (rural)</t>
+  </si>
+  <si>
+    <t>Índice dep. econ. H (rural)</t>
+  </si>
+  <si>
+    <t>Índice dep. econ. M (rural)</t>
   </si>
 </sst>
 </file>
@@ -1575,14 +1617,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B198"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B208"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1590,7 +1632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1598,7 +1640,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1606,7 +1648,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1614,7 +1656,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1622,7 +1664,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1630,7 +1672,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1638,7 +1680,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1646,7 +1688,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1654,7 +1696,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1662,7 +1704,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1670,7 +1712,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1678,7 +1720,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1686,7 +1728,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1694,7 +1736,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1702,7 +1744,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1710,7 +1752,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1718,7 +1760,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1726,7 +1768,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1734,7 +1776,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1742,7 +1784,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1750,7 +1792,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -1758,7 +1800,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1766,7 +1808,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1774,7 +1816,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -1782,7 +1824,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -1790,7 +1832,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -1798,7 +1840,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -1806,7 +1848,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -1814,7 +1856,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -1822,7 +1864,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -1830,7 +1872,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -1838,7 +1880,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -1846,7 +1888,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -1854,7 +1896,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -1862,7 +1904,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -1870,7 +1912,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -1878,7 +1920,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -1886,7 +1928,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -1894,7 +1936,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -1902,7 +1944,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -1910,7 +1952,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -1918,7 +1960,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -1926,7 +1968,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -1934,7 +1976,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -1942,7 +1984,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>46</v>
       </c>
@@ -1950,7 +1992,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -1958,7 +2000,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -1966,7 +2008,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -1974,7 +2016,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -1982,7 +2024,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>51</v>
       </c>
@@ -1990,7 +2032,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>52</v>
       </c>
@@ -1998,7 +2040,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>53</v>
       </c>
@@ -2006,7 +2048,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>54</v>
       </c>
@@ -2014,7 +2056,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>55</v>
       </c>
@@ -2022,7 +2064,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>56</v>
       </c>
@@ -2030,7 +2072,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>57</v>
       </c>
@@ -2038,7 +2080,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -2046,7 +2088,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>59</v>
       </c>
@@ -2054,7 +2096,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>60</v>
       </c>
@@ -2062,7 +2104,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>61</v>
       </c>
@@ -2070,7 +2112,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>62</v>
       </c>
@@ -2078,7 +2120,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>63</v>
       </c>
@@ -2086,7 +2128,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>64</v>
       </c>
@@ -2094,7 +2136,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>65</v>
       </c>
@@ -2102,7 +2144,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>66</v>
       </c>
@@ -2110,7 +2152,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>67</v>
       </c>
@@ -2118,7 +2160,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>68</v>
       </c>
@@ -2126,7 +2168,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>69</v>
       </c>
@@ -2134,7 +2176,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>70</v>
       </c>
@@ -2142,7 +2184,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>71</v>
       </c>
@@ -2150,7 +2192,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>72</v>
       </c>
@@ -2158,7 +2200,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>73</v>
       </c>
@@ -2166,7 +2208,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>74</v>
       </c>
@@ -2174,7 +2216,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>75</v>
       </c>
@@ -2182,7 +2224,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>76</v>
       </c>
@@ -2190,7 +2232,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>77</v>
       </c>
@@ -2198,7 +2240,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>78</v>
       </c>
@@ -2206,7 +2248,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>79</v>
       </c>
@@ -2214,7 +2256,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>80</v>
       </c>
@@ -2222,7 +2264,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>81</v>
       </c>
@@ -2230,7 +2272,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>82</v>
       </c>
@@ -2238,7 +2280,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -2246,7 +2288,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>84</v>
       </c>
@@ -2254,7 +2296,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>85</v>
       </c>
@@ -2262,7 +2304,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>86</v>
       </c>
@@ -2270,7 +2312,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>87</v>
       </c>
@@ -2278,7 +2320,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>88</v>
       </c>
@@ -2286,7 +2328,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>89</v>
       </c>
@@ -2294,7 +2336,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>90</v>
       </c>
@@ -2302,7 +2344,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>91</v>
       </c>
@@ -2310,7 +2352,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>92</v>
       </c>
@@ -2318,7 +2360,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>93</v>
       </c>
@@ -2326,7 +2368,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>94</v>
       </c>
@@ -2334,7 +2376,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>95</v>
       </c>
@@ -2342,7 +2384,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>96</v>
       </c>
@@ -2350,7 +2392,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>97</v>
       </c>
@@ -2358,7 +2400,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>98</v>
       </c>
@@ -2366,7 +2408,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>99</v>
       </c>
@@ -2374,7 +2416,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>100</v>
       </c>
@@ -2382,7 +2424,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>101</v>
       </c>
@@ -2390,7 +2432,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>102</v>
       </c>
@@ -2398,7 +2440,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>103</v>
       </c>
@@ -2406,7 +2448,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>104</v>
       </c>
@@ -2414,7 +2456,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>105</v>
       </c>
@@ -2422,7 +2464,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>106</v>
       </c>
@@ -2430,7 +2472,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>107</v>
       </c>
@@ -2438,7 +2480,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>108</v>
       </c>
@@ -2446,7 +2488,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>109</v>
       </c>
@@ -2454,7 +2496,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>110</v>
       </c>
@@ -2462,7 +2504,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>111</v>
       </c>
@@ -2470,7 +2512,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>112</v>
       </c>
@@ -2478,7 +2520,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>113</v>
       </c>
@@ -2486,7 +2528,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>114</v>
       </c>
@@ -2494,7 +2536,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>115</v>
       </c>
@@ -2502,7 +2544,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>116</v>
       </c>
@@ -2510,7 +2552,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>117</v>
       </c>
@@ -2518,7 +2560,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>118</v>
       </c>
@@ -2526,7 +2568,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>119</v>
       </c>
@@ -2534,7 +2576,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>120</v>
       </c>
@@ -2542,7 +2584,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>121</v>
       </c>
@@ -2550,7 +2592,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>122</v>
       </c>
@@ -2558,7 +2600,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>123</v>
       </c>
@@ -2566,7 +2608,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>124</v>
       </c>
@@ -2574,7 +2616,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>125</v>
       </c>
@@ -2582,7 +2624,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>126</v>
       </c>
@@ -2590,7 +2632,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>127</v>
       </c>
@@ -2598,7 +2640,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>128</v>
       </c>
@@ -2606,7 +2648,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>129</v>
       </c>
@@ -2614,7 +2656,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>130</v>
       </c>
@@ -2622,7 +2664,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>131</v>
       </c>
@@ -2630,7 +2672,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>132</v>
       </c>
@@ -2638,7 +2680,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>133</v>
       </c>
@@ -2646,7 +2688,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>134</v>
       </c>
@@ -2654,7 +2696,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>135</v>
       </c>
@@ -2662,7 +2704,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>136</v>
       </c>
@@ -2670,7 +2712,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>137</v>
       </c>
@@ -2678,7 +2720,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>138</v>
       </c>
@@ -2686,7 +2728,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>139</v>
       </c>
@@ -2694,7 +2736,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>140</v>
       </c>
@@ -2702,7 +2744,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>141</v>
       </c>
@@ -2710,7 +2752,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>142</v>
       </c>
@@ -2718,7 +2760,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>143</v>
       </c>
@@ -2726,7 +2768,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>144</v>
       </c>
@@ -2734,7 +2776,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>145</v>
       </c>
@@ -2742,7 +2784,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>146</v>
       </c>
@@ -2750,7 +2792,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>147</v>
       </c>
@@ -2758,7 +2800,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>148</v>
       </c>
@@ -2766,7 +2808,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>149</v>
       </c>
@@ -2774,7 +2816,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>150</v>
       </c>
@@ -2782,7 +2824,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>151</v>
       </c>
@@ -2790,7 +2832,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>152</v>
       </c>
@@ -2798,7 +2840,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>153</v>
       </c>
@@ -2806,7 +2848,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>154</v>
       </c>
@@ -2814,7 +2856,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>155</v>
       </c>
@@ -2822,7 +2864,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>156</v>
       </c>
@@ -2830,7 +2872,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>157</v>
       </c>
@@ -2838,7 +2880,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>158</v>
       </c>
@@ -2846,7 +2888,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>159</v>
       </c>
@@ -2854,7 +2896,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>160</v>
       </c>
@@ -2862,7 +2904,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>161</v>
       </c>
@@ -2870,7 +2912,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>162</v>
       </c>
@@ -2878,7 +2920,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>163</v>
       </c>
@@ -2886,7 +2928,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>164</v>
       </c>
@@ -2894,7 +2936,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>165</v>
       </c>
@@ -2902,7 +2944,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>166</v>
       </c>
@@ -2910,7 +2952,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>167</v>
       </c>
@@ -2918,7 +2960,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>168</v>
       </c>
@@ -2926,7 +2968,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>169</v>
       </c>
@@ -2934,7 +2976,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>170</v>
       </c>
@@ -2942,7 +2984,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>171</v>
       </c>
@@ -2950,7 +2992,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>172</v>
       </c>
@@ -2958,7 +3000,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>173</v>
       </c>
@@ -2966,7 +3008,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>174</v>
       </c>
@@ -2974,7 +3016,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>175</v>
       </c>
@@ -2982,7 +3024,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>176</v>
       </c>
@@ -2990,7 +3032,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>177</v>
       </c>
@@ -2998,7 +3040,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>178</v>
       </c>
@@ -3006,7 +3048,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>179</v>
       </c>
@@ -3014,7 +3056,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>180</v>
       </c>
@@ -3022,7 +3064,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>181</v>
       </c>
@@ -3030,7 +3072,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>182</v>
       </c>
@@ -3038,7 +3080,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>183</v>
       </c>
@@ -3046,7 +3088,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>184</v>
       </c>
@@ -3054,7 +3096,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>185</v>
       </c>
@@ -3062,7 +3104,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>186</v>
       </c>
@@ -3070,7 +3112,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>187</v>
       </c>
@@ -3078,7 +3120,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>188</v>
       </c>
@@ -3086,7 +3128,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>189</v>
       </c>
@@ -3094,7 +3136,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>190</v>
       </c>
@@ -3102,7 +3144,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>191</v>
       </c>
@@ -3110,7 +3152,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>192</v>
       </c>
@@ -3118,7 +3160,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>193</v>
       </c>
@@ -3126,7 +3168,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>194</v>
       </c>
@@ -3134,7 +3176,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>195</v>
       </c>
@@ -3142,7 +3184,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>196</v>
       </c>
@@ -3150,7 +3192,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>197</v>
       </c>
@@ -3158,12 +3200,92 @@
         <v>394</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>198</v>
       </c>
       <c r="B198" t="s">
         <v>395</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>166</v>
+      </c>
+      <c r="B199" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>167</v>
+      </c>
+      <c r="B200" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>168</v>
+      </c>
+      <c r="B201" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>401</v>
+      </c>
+      <c r="B202" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>399</v>
+      </c>
+      <c r="B203" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>400</v>
+      </c>
+      <c r="B204" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>402</v>
+      </c>
+      <c r="B205" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>404</v>
+      </c>
+      <c r="B206" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>405</v>
+      </c>
+      <c r="B207" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>406</v>
+      </c>
+      <c r="B208" t="s">
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -3172,6 +3294,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001A7765192ECBF642B9941230C1216E50" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4f9b497815717cd7d6cdc8413a0649bd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="97399761-d0fd-4473-af46-db46fcae3ae6" xmlns:ns3="043d79eb-2b3a-4fe9-bdb7-cdfc642b4baf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5abb4445fbbe144c1dbe287b6077d1f6" ns2:_="" ns3:_="">
     <xsd:import namespace="97399761-d0fd-4473-af46-db46fcae3ae6"/>
@@ -3360,15 +3491,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3381,13 +3503,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA35FEF2-9BE6-486B-A35F-F735D0671FCA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{190FB101-A7A0-4750-A330-E7E683F1D1C2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{190FB101-A7A0-4750-A330-E7E683F1D1C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA35FEF2-9BE6-486B-A35F-F735D0671FCA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="97399761-d0fd-4473-af46-db46fcae3ae6"/>
+    <ds:schemaRef ds:uri="043d79eb-2b3a-4fe9-bdb7-cdfc642b4baf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAB02C99-CC52-40CD-9C4B-02C519DC64F6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAB02C99-CC52-40CD-9C4B-02C519DC64F6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="97399761-d0fd-4473-af46-db46fcae3ae6"/>
+    <ds:schemaRef ds:uri="043d79eb-2b3a-4fe9-bdb7-cdfc642b4baf"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>